--- a/frontend/test_data/header_detection/Unpredictable_Headers_Test.xlsx
+++ b/frontend/test_data/header_detection/Unpredictable_Headers_Test.xlsx
@@ -479,7 +479,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:M5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -498,18 +498,27 @@
         <v>Consistent String Signal</v>
       </c>
       <c r="F1" t="str">
+        <v>Consistent Numeric Signal</v>
+      </c>
+      <c r="G1" t="str">
         <v>Pure Data Penalty</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
+        <v>Numeric Data Penalty</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Pivoted Series Bonus</v>
+      </c>
+      <c r="J1" t="str">
         <v>100% String Bonus</v>
       </c>
-      <c r="H1" t="str">
+      <c r="K1" t="str">
         <v>Unique Values Rule</v>
       </c>
-      <c r="I1" t="str">
+      <c r="L1" t="str">
         <v>Orphan Header Penalty</v>
       </c>
-      <c r="J1" t="str">
+      <c r="M1" t="str">
         <v>TOTAL SCORE</v>
       </c>
     </row>
@@ -533,15 +542,24 @@
         <v>0</v>
       </c>
       <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
         <v>10</v>
       </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
         <v>17</v>
       </c>
     </row>
@@ -565,15 +583,24 @@
         <v>0</v>
       </c>
       <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
         <v>10</v>
       </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
         <v>17</v>
       </c>
     </row>
@@ -588,25 +615,34 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="E4">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
         <v>10</v>
       </c>
-      <c r="H4">
+      <c r="K4">
         <v>5</v>
       </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>87</v>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>63</v>
       </c>
     </row>
     <row r="5">
@@ -623,7 +659,7 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -632,18 +668,27 @@
         <v>0</v>
       </c>
       <c r="H5">
+        <v>-20</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
         <v>5</v>
       </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>32</v>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/frontend/test_data/header_detection/Unpredictable_Headers_Test.xlsx
+++ b/frontend/test_data/header_detection/Unpredictable_Headers_Test.xlsx
@@ -479,7 +479,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:N5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -489,37 +489,40 @@
         <v>Row Preview</v>
       </c>
       <c r="C1" t="str">
-        <v>Density Bonus</v>
+        <v>Pillar 1: Density (%)</v>
       </c>
       <c r="D1" t="str">
-        <v>Data Boundary Signal</v>
+        <v>Pillar 2: Boundary (%)</v>
       </c>
       <c r="E1" t="str">
-        <v>Consistent String Signal</v>
+        <v>Pillar 3: Consistency (%)</v>
       </c>
       <c r="F1" t="str">
-        <v>Consistent Numeric Signal</v>
+        <v>Pillar 4: Traits (%)</v>
       </c>
       <c r="G1" t="str">
         <v>Pure Data Penalty</v>
       </c>
       <c r="H1" t="str">
-        <v>Numeric Data Penalty</v>
+        <v>Mixed Data Penalty</v>
       </c>
       <c r="I1" t="str">
-        <v>Pivoted Series Bonus</v>
+        <v>Search Booster (Pivoted)</v>
       </c>
       <c r="J1" t="str">
-        <v>100% String Bonus</v>
+        <v>Orphan Header Penalty</v>
       </c>
       <c r="K1" t="str">
-        <v>Unique Values Rule</v>
+        <v>Duplicates Penalty</v>
       </c>
       <c r="L1" t="str">
-        <v>Orphan Header Penalty</v>
+        <v>FILLED CELLS</v>
       </c>
       <c r="M1" t="str">
-        <v>TOTAL SCORE</v>
+        <v>TOTAL RAW SCORE</v>
+      </c>
+      <c r="N1" t="str">
+        <v>NORMALIZED SCORE (%)</v>
       </c>
     </row>
     <row r="2">
@@ -530,16 +533,16 @@
         <v>["Random Notes"]</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -551,16 +554,19 @@
         <v>0</v>
       </c>
       <c r="J2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>17</v>
+        <v>48</v>
+      </c>
+      <c r="N2">
+        <v>48</v>
       </c>
     </row>
     <row r="3">
@@ -571,16 +577,16 @@
         <v>["Legacy Export 9001"]</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -592,16 +598,19 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>17</v>
+        <v>48</v>
+      </c>
+      <c r="N3">
+        <v>48</v>
       </c>
     </row>
     <row r="4">
@@ -612,16 +621,16 @@
         <v>["Alpha_Num","Entity_Title","Loc_String","Zip_Post</v>
       </c>
       <c r="C4">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D4">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -633,16 +642,19 @@
         <v>0</v>
       </c>
       <c r="J4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M4">
-        <v>63</v>
+        <v>76</v>
+      </c>
+      <c r="N4">
+        <v>76</v>
       </c>
     </row>
     <row r="5">
@@ -653,22 +665,22 @@
         <v>["V001","Acme Corp","Austin TX","78701","5000","10</v>
       </c>
       <c r="C5">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H5">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -677,18 +689,21 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>6</v>
+        <v>-64</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/frontend/test_data/header_detection/Unpredictable_Headers_Test.xlsx
+++ b/frontend/test_data/header_detection/Unpredictable_Headers_Test.xlsx
@@ -479,7 +479,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:M5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -507,21 +507,18 @@
         <v>Mixed Data Penalty</v>
       </c>
       <c r="I1" t="str">
-        <v>Search Booster (Pivoted)</v>
+        <v>Orphan Header Penalty</v>
       </c>
       <c r="J1" t="str">
-        <v>Orphan Header Penalty</v>
+        <v>Duplicates Penalty</v>
       </c>
       <c r="K1" t="str">
-        <v>Duplicates Penalty</v>
+        <v>FILLED CELLS</v>
       </c>
       <c r="L1" t="str">
-        <v>FILLED CELLS</v>
+        <v>TOTAL RAW SCORE</v>
       </c>
       <c r="M1" t="str">
-        <v>TOTAL RAW SCORE</v>
-      </c>
-      <c r="N1" t="str">
         <v>NORMALIZED SCORE (%)</v>
       </c>
     </row>
@@ -557,15 +554,12 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="M2">
-        <v>48</v>
-      </c>
-      <c r="N2">
         <v>48</v>
       </c>
     </row>
@@ -601,15 +595,12 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="M3">
-        <v>48</v>
-      </c>
-      <c r="N3">
         <v>48</v>
       </c>
     </row>
@@ -645,15 +636,12 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L4">
-        <v>6</v>
+        <v>76</v>
       </c>
       <c r="M4">
-        <v>76</v>
-      </c>
-      <c r="N4">
         <v>76</v>
       </c>
     </row>
@@ -689,21 +677,18 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L5">
-        <v>6</v>
+        <v>-64</v>
       </c>
       <c r="M5">
-        <v>-64</v>
-      </c>
-      <c r="N5">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M5"/>
   </ignoredErrors>
 </worksheet>
 </file>